--- a/06_TPCvIKT/output/em_nb_summary.xlsx
+++ b/06_TPCvIKT/output/em_nb_summary.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="EM-NB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Distortion" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">ik</t>
   </si>
@@ -75,6 +76,24 @@
   </si>
   <si>
     <t xml:space="preserve">mean_em_V_pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cash_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ik_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ik_coefficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_pal_basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distortion_pesos</t>
   </si>
 </sst>
 </file>
@@ -468,6 +487,187 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.831972789115646</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.377049180327869</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0948158253751705</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.576975476839237</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.108310626702997</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.901773533424284</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.562113932738504</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.876106194690266</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.887602179836512</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.96548691734402</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.707123640746273</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.836640287690508</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.628298400839683</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.848981131883865</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.954071051720666</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.884637361357582</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.995572261069239</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.9978300077231</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.19416157501697</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.555980224099697</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.573571428571429</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.309728183118741</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.09087656529517</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.448928571428571</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0731182795698925</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.494767232046193</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.448040273282992</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.632048536759457</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.721761097076868</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.910327521729774</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.689798786794965</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.801681101815445</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.625099437891979</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.819816175811267</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.792542456116192</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.828384468716885</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.987350366985849</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.997716250051046</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.7673672960456</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.328072358601922</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.555980224099697</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.328072358601922</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.227907865497775</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.227907865497778</v>
+      </c>
+      <c r="E2" t="n">
+        <v>205.942039269192</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.9358105861011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
